--- a/simulations/phenol_nitrous_oxide/economics_phenol_N2O.xlsx
+++ b/simulations/phenol_nitrous_oxide/economics_phenol_N2O.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\phenol_nitrous_oxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B76755-2597-410C-936E-44F78F891512}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05EB0A2-D75E-4A0F-8AC4-AAB8B2CDED53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="132">
   <si>
     <t>Cost factors</t>
   </si>
@@ -603,9 +603,6 @@
   </si>
   <si>
     <t>Green</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -2303,7 +2300,9 @@
     <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.28515625" style="11" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="11"/>
+    <col min="10" max="11" width="8.85546875" style="11"/>
+    <col min="12" max="13" width="9.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
@@ -2477,11 +2476,11 @@
       <c r="K8" s="40">
         <v>879</v>
       </c>
-      <c r="L8" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>132</v>
+      <c r="L8" s="40">
+        <v>682</v>
+      </c>
+      <c r="M8" s="40">
+        <v>579</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
@@ -2501,11 +2500,11 @@
       <c r="K9" s="40">
         <v>1465</v>
       </c>
-      <c r="L9" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="M9" s="40" t="s">
-        <v>132</v>
+      <c r="L9" s="40">
+        <v>909</v>
+      </c>
+      <c r="M9" s="40">
+        <v>1015</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">

--- a/simulations/phenol_nitrous_oxide/economics_phenol_N2O.xlsx
+++ b/simulations/phenol_nitrous_oxide/economics_phenol_N2O.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\phenol_nitrous_oxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05EB0A2-D75E-4A0F-8AC4-AAB8B2CDED53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229462F9-24ED-4DA1-83F1-EAD21D976A56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -763,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -888,6 +888,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1377,16 +1378,16 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
       <c r="N13" s="32" t="s">
         <v>88</v>
       </c>
@@ -1689,16 +1690,16 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="60"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -1729,16 +1730,16 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="57"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
@@ -1797,16 +1798,16 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -2098,11 +2099,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="60">
+      <c r="A3" s="61">
         <v>2022</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
@@ -2116,11 +2117,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -2159,19 +2160,19 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
-      <c r="B9" s="56"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -2186,19 +2187,19 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="28">
         <f>C11</f>
         <v>1.595036343502283</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -2225,19 +2226,19 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="28">
         <f>SUM(C14:C15)</f>
         <v>7.1905447043117965</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="57"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -2252,18 +2253,18 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="17">
         <f>C18</f>
         <v>0.87088984355224663</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
         <v>16.997095891366325</v>
@@ -2335,13 +2336,13 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="57"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="47" t="s">
@@ -2392,7 +2393,7 @@
         <f>D6*E6</f>
         <v>24854.867590318481</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="54">
         <f>F6/Summary!$C$23</f>
         <v>0.66279646911249523</v>
       </c>
@@ -2420,15 +2421,15 @@
         <v>17.825248463383101</v>
       </c>
       <c r="E7" s="40">
-        <v>635.64706468633074</v>
+        <v>520</v>
       </c>
       <c r="F7" s="40">
         <f>D7*E7</f>
-        <v>11330.566863053995</v>
-      </c>
-      <c r="G7" s="11">
+        <v>9269.1292009592125</v>
+      </c>
+      <c r="G7" s="54">
         <f>F7/Summary!$C$23</f>
-        <v>0.30214844969846011</v>
+        <v>0.2471767787061693</v>
       </c>
       <c r="I7" s="47" t="s">
         <v>129</v>
@@ -2463,7 +2464,7 @@
         <f>D8*E8</f>
         <v>20635.919637143154</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="54">
         <f>F8/Summary!$C$23</f>
         <v>0.55029119035481566</v>
       </c>
@@ -2476,21 +2477,22 @@
       <c r="K8" s="40">
         <v>879</v>
       </c>
-      <c r="L8" s="40">
-        <v>682</v>
+      <c r="L8" s="39">
+        <v>394</v>
       </c>
       <c r="M8" s="40">
         <v>579</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="54"/>
       <c r="I9" s="47" t="s">
         <v>112</v>
       </c>
@@ -2500,8 +2502,8 @@
       <c r="K9" s="40">
         <v>1465</v>
       </c>
-      <c r="L9" s="40">
-        <v>909</v>
+      <c r="L9" s="39">
+        <v>520</v>
       </c>
       <c r="M9" s="40">
         <v>1015</v>
@@ -2525,7 +2527,7 @@
         <f>D10*E10</f>
         <v>18.739826549260084</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="54">
         <f>F10/Summary!$C$23</f>
         <v>4.9972870800841899E-4</v>
       </c>
@@ -2539,7 +2541,7 @@
         <v>1157.6792143758207</v>
       </c>
       <c r="L10" s="40">
-        <v>795</v>
+        <v>457</v>
       </c>
       <c r="M10" s="40">
         <v>797</v>
@@ -2562,7 +2564,7 @@
         <f>D11*E11</f>
         <v>2931.9068041692162</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="54">
         <f>F11/Summary!$C$23</f>
         <v>7.8184181448916604E-2</v>
       </c>
@@ -2585,7 +2587,7 @@
         <f>D12*E12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="54">
         <f>F12/Summary!$C$23</f>
         <v>0</v>
       </c>
@@ -2602,7 +2604,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19">
         <f>(F5+F6+F7+F10+F11)/1000000*8000</f>
-        <v>313.08864867272763</v>
+        <v>296.59714737596931</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
@@ -2683,14 +2685,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="F2" s="60" t="s">
+      <c r="C2" s="61"/>
+      <c r="F2" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="60"/>
+      <c r="G2" s="61"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
@@ -2965,7 +2967,7 @@
       </c>
       <c r="C20" s="17">
         <f>OPEX!F13</f>
-        <v>313.08864867272763</v>
+        <v>296.59714737596931</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>85</v>
@@ -2981,7 +2983,7 @@
       </c>
       <c r="C21" s="17">
         <f>(C18+C19+C20)</f>
-        <v>327.27689234765722</v>
+        <v>310.78539105089891</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>94</v>
@@ -2997,7 +2999,7 @@
       </c>
       <c r="C22" s="17">
         <f>(C21)*1000000/8000</f>
-        <v>40909.611543457147</v>
+        <v>38848.173881362367</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>93</v>
@@ -3027,7 +3029,7 @@
       </c>
       <c r="C24" s="42">
         <f>C22/C23</f>
-        <v>1.0909229745536431</v>
+        <v>1.0359513035613523</v>
       </c>
       <c r="F24" s="29" t="s">
         <v>105</v>
